--- a/material_control/data/동호인덱스.xlsx
+++ b/material_control/data/동호인덱스.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\source\pygame\material_control\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\pygame\pygame\material_control\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A952C63A-837E-472F-969A-21B9F8EB18C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E3F5D4-19AA-4F32-9FB3-3902D0B6F9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="270" yWindow="2610" windowWidth="25455" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="종합아파트 검침표" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>동</t>
-  </si>
-  <si>
-    <t>호</t>
-  </si>
   <si>
     <t>소방</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -69,6 +63,14 @@
   </si>
   <si>
     <t>기타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>dong</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ho</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -441,20 +443,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B861"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -462,7 +464,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>101</v>
       </c>
@@ -470,7 +472,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>101</v>
       </c>
@@ -478,7 +480,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>101</v>
       </c>
@@ -486,7 +488,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>101</v>
       </c>
@@ -494,7 +496,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>101</v>
       </c>
@@ -502,7 +504,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>101</v>
       </c>
@@ -510,7 +512,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>101</v>
       </c>
@@ -518,7 +520,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>101</v>
       </c>
@@ -526,7 +528,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>101</v>
       </c>
@@ -534,7 +536,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>101</v>
       </c>
@@ -542,7 +544,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>101</v>
       </c>
@@ -550,7 +552,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>101</v>
       </c>
@@ -558,7 +560,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>101</v>
       </c>
@@ -566,7 +568,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>101</v>
       </c>
@@ -574,7 +576,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>101</v>
       </c>
@@ -582,7 +584,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>101</v>
       </c>
@@ -590,7 +592,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>101</v>
       </c>
@@ -598,7 +600,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>101</v>
       </c>
@@ -606,7 +608,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>101</v>
       </c>
@@ -614,7 +616,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>101</v>
       </c>
@@ -622,7 +624,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>101</v>
       </c>
@@ -630,7 +632,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>101</v>
       </c>
@@ -638,7 +640,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>101</v>
       </c>
@@ -646,7 +648,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>101</v>
       </c>
@@ -654,7 +656,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>101</v>
       </c>
@@ -662,7 +664,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>101</v>
       </c>
@@ -670,7 +672,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>101</v>
       </c>
@@ -678,7 +680,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>101</v>
       </c>
@@ -686,7 +688,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>101</v>
       </c>
@@ -694,7 +696,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>101</v>
       </c>
@@ -702,7 +704,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>101</v>
       </c>
@@ -710,7 +712,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>101</v>
       </c>
@@ -718,7 +720,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>101</v>
       </c>
@@ -726,7 +728,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>101</v>
       </c>
@@ -734,7 +736,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>101</v>
       </c>
@@ -742,7 +744,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>101</v>
       </c>
@@ -750,7 +752,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>101</v>
       </c>
@@ -758,7 +760,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>101</v>
       </c>
@@ -766,7 +768,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>101</v>
       </c>
@@ -774,7 +776,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>101</v>
       </c>
@@ -782,7 +784,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>101</v>
       </c>
@@ -790,7 +792,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>101</v>
       </c>
@@ -798,7 +800,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>101</v>
       </c>
@@ -806,7 +808,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>101</v>
       </c>
@@ -814,7 +816,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>101</v>
       </c>
@@ -822,7 +824,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>101</v>
       </c>
@@ -830,7 +832,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>101</v>
       </c>
@@ -838,7 +840,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>101</v>
       </c>
@@ -846,7 +848,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>101</v>
       </c>
@@ -854,7 +856,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>101</v>
       </c>
@@ -862,7 +864,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>101</v>
       </c>
@@ -870,7 +872,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>101</v>
       </c>
@@ -878,7 +880,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>101</v>
       </c>
@@ -886,7 +888,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>101</v>
       </c>
@@ -894,7 +896,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>101</v>
       </c>
@@ -902,7 +904,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>101</v>
       </c>
@@ -910,7 +912,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>101</v>
       </c>
@@ -918,7 +920,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>101</v>
       </c>
@@ -926,7 +928,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>101</v>
       </c>
@@ -934,7 +936,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>101</v>
       </c>
@@ -942,7 +944,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>101</v>
       </c>
@@ -950,7 +952,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>101</v>
       </c>
@@ -958,7 +960,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>101</v>
       </c>
@@ -966,7 +968,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>101</v>
       </c>
@@ -974,7 +976,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>101</v>
       </c>
@@ -982,7 +984,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>101</v>
       </c>
@@ -990,7 +992,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>101</v>
       </c>
@@ -998,7 +1000,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>102</v>
       </c>
@@ -1006,7 +1008,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>102</v>
       </c>
@@ -1014,7 +1016,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>102</v>
       </c>
@@ -1022,7 +1024,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>102</v>
       </c>
@@ -1030,7 +1032,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>102</v>
       </c>
@@ -1038,7 +1040,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>102</v>
       </c>
@@ -1046,7 +1048,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>102</v>
       </c>
@@ -1054,7 +1056,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>102</v>
       </c>
@@ -1062,7 +1064,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>102</v>
       </c>
@@ -1070,7 +1072,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>102</v>
       </c>
@@ -1078,7 +1080,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>102</v>
       </c>
@@ -1086,7 +1088,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>102</v>
       </c>
@@ -1094,7 +1096,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>102</v>
       </c>
@@ -1102,7 +1104,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>102</v>
       </c>
@@ -1110,7 +1112,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>102</v>
       </c>
@@ -1118,7 +1120,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>102</v>
       </c>
@@ -1126,7 +1128,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>102</v>
       </c>
@@ -1134,7 +1136,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>102</v>
       </c>
@@ -1142,7 +1144,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>102</v>
       </c>
@@ -1150,7 +1152,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>102</v>
       </c>
@@ -1158,7 +1160,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>102</v>
       </c>
@@ -1166,7 +1168,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>102</v>
       </c>
@@ -1174,7 +1176,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>102</v>
       </c>
@@ -1182,7 +1184,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>102</v>
       </c>
@@ -1190,7 +1192,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>102</v>
       </c>
@@ -1198,7 +1200,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>102</v>
       </c>
@@ -1206,7 +1208,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>102</v>
       </c>
@@ -1214,7 +1216,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>102</v>
       </c>
@@ -1222,7 +1224,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>102</v>
       </c>
@@ -1230,7 +1232,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>102</v>
       </c>
@@ -1238,7 +1240,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>102</v>
       </c>
@@ -1246,7 +1248,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>102</v>
       </c>
@@ -1254,7 +1256,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>102</v>
       </c>
@@ -1262,7 +1264,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -1270,7 +1272,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>102</v>
       </c>
@@ -1278,7 +1280,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>102</v>
       </c>
@@ -1286,7 +1288,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>102</v>
       </c>
@@ -1294,7 +1296,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>102</v>
       </c>
@@ -1302,7 +1304,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>102</v>
       </c>
@@ -1310,7 +1312,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>102</v>
       </c>
@@ -1318,7 +1320,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>102</v>
       </c>
@@ -1326,7 +1328,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>102</v>
       </c>
@@ -1334,7 +1336,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>102</v>
       </c>
@@ -1342,7 +1344,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>102</v>
       </c>
@@ -1350,7 +1352,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>102</v>
       </c>
@@ -1358,7 +1360,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>102</v>
       </c>
@@ -1366,7 +1368,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>102</v>
       </c>
@@ -1374,7 +1376,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>102</v>
       </c>
@@ -1382,7 +1384,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>102</v>
       </c>
@@ -1390,7 +1392,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>102</v>
       </c>
@@ -1398,7 +1400,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>102</v>
       </c>
@@ -1406,7 +1408,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>102</v>
       </c>
@@ -1414,7 +1416,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>102</v>
       </c>
@@ -1422,7 +1424,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>102</v>
       </c>
@@ -1430,7 +1432,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>102</v>
       </c>
@@ -1438,7 +1440,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>102</v>
       </c>
@@ -1446,7 +1448,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>102</v>
       </c>
@@ -1454,7 +1456,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>102</v>
       </c>
@@ -1462,7 +1464,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>102</v>
       </c>
@@ -1470,7 +1472,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>102</v>
       </c>
@@ -1478,7 +1480,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>102</v>
       </c>
@@ -1486,7 +1488,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>102</v>
       </c>
@@ -1494,7 +1496,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>102</v>
       </c>
@@ -1502,7 +1504,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>102</v>
       </c>
@@ -1510,7 +1512,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>102</v>
       </c>
@@ -1518,7 +1520,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>102</v>
       </c>
@@ -1526,7 +1528,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>102</v>
       </c>
@@ -1534,7 +1536,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>102</v>
       </c>
@@ -1542,7 +1544,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>102</v>
       </c>
@@ -1550,7 +1552,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>102</v>
       </c>
@@ -1558,7 +1560,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>102</v>
       </c>
@@ -1566,7 +1568,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>102</v>
       </c>
@@ -1574,7 +1576,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>102</v>
       </c>
@@ -1582,7 +1584,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>102</v>
       </c>
@@ -1590,7 +1592,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>103</v>
       </c>
@@ -1598,7 +1600,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>103</v>
       </c>
@@ -1606,7 +1608,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>103</v>
       </c>
@@ -1614,7 +1616,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>103</v>
       </c>
@@ -1622,7 +1624,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>103</v>
       </c>
@@ -1630,7 +1632,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>103</v>
       </c>
@@ -1638,7 +1640,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>103</v>
       </c>
@@ -1646,7 +1648,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>103</v>
       </c>
@@ -1654,7 +1656,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>103</v>
       </c>
@@ -1662,7 +1664,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>103</v>
       </c>
@@ -1670,7 +1672,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>103</v>
       </c>
@@ -1678,7 +1680,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>103</v>
       </c>
@@ -1686,7 +1688,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>103</v>
       </c>
@@ -1694,7 +1696,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>103</v>
       </c>
@@ -1702,7 +1704,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>103</v>
       </c>
@@ -1710,7 +1712,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>103</v>
       </c>
@@ -1718,7 +1720,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>103</v>
       </c>
@@ -1726,7 +1728,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>103</v>
       </c>
@@ -1734,7 +1736,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>103</v>
       </c>
@@ -1742,7 +1744,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>103</v>
       </c>
@@ -1750,7 +1752,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>103</v>
       </c>
@@ -1758,7 +1760,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>103</v>
       </c>
@@ -1766,7 +1768,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>103</v>
       </c>
@@ -1774,7 +1776,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>103</v>
       </c>
@@ -1782,7 +1784,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>103</v>
       </c>
@@ -1790,7 +1792,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>103</v>
       </c>
@@ -1798,7 +1800,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>103</v>
       </c>
@@ -1806,7 +1808,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>103</v>
       </c>
@@ -1814,7 +1816,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>103</v>
       </c>
@@ -1822,7 +1824,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>103</v>
       </c>
@@ -1830,7 +1832,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>103</v>
       </c>
@@ -1838,7 +1840,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>103</v>
       </c>
@@ -1846,7 +1848,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>103</v>
       </c>
@@ -1854,7 +1856,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>103</v>
       </c>
@@ -1862,7 +1864,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>103</v>
       </c>
@@ -1870,7 +1872,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>103</v>
       </c>
@@ -1878,7 +1880,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>103</v>
       </c>
@@ -1886,7 +1888,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>103</v>
       </c>
@@ -1894,7 +1896,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>103</v>
       </c>
@@ -1902,7 +1904,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>103</v>
       </c>
@@ -1910,7 +1912,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>103</v>
       </c>
@@ -1918,7 +1920,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>103</v>
       </c>
@@ -1926,7 +1928,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>103</v>
       </c>
@@ -1934,7 +1936,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>103</v>
       </c>
@@ -1942,7 +1944,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>103</v>
       </c>
@@ -1950,7 +1952,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>103</v>
       </c>
@@ -1958,7 +1960,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>103</v>
       </c>
@@ -1966,7 +1968,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>103</v>
       </c>
@@ -1974,7 +1976,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>103</v>
       </c>
@@ -1982,7 +1984,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>103</v>
       </c>
@@ -1990,7 +1992,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>103</v>
       </c>
@@ -1998,7 +2000,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>103</v>
       </c>
@@ -2006,7 +2008,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>103</v>
       </c>
@@ -2014,7 +2016,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>103</v>
       </c>
@@ -2022,7 +2024,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>103</v>
       </c>
@@ -2030,7 +2032,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>103</v>
       </c>
@@ -2038,7 +2040,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>103</v>
       </c>
@@ -2046,7 +2048,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>103</v>
       </c>
@@ -2054,7 +2056,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>103</v>
       </c>
@@ -2062,7 +2064,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>103</v>
       </c>
@@ -2070,7 +2072,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>103</v>
       </c>
@@ -2078,7 +2080,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>103</v>
       </c>
@@ -2086,7 +2088,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>103</v>
       </c>
@@ -2094,7 +2096,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>103</v>
       </c>
@@ -2102,7 +2104,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>103</v>
       </c>
@@ -2110,7 +2112,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>103</v>
       </c>
@@ -2118,7 +2120,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>103</v>
       </c>
@@ -2126,7 +2128,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>103</v>
       </c>
@@ -2134,7 +2136,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>103</v>
       </c>
@@ -2142,7 +2144,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>103</v>
       </c>
@@ -2150,7 +2152,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>103</v>
       </c>
@@ -2158,7 +2160,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>104</v>
       </c>
@@ -2166,7 +2168,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>104</v>
       </c>
@@ -2174,7 +2176,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>104</v>
       </c>
@@ -2182,7 +2184,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>104</v>
       </c>
@@ -2190,7 +2192,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>104</v>
       </c>
@@ -2198,7 +2200,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>104</v>
       </c>
@@ -2206,7 +2208,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>104</v>
       </c>
@@ -2214,7 +2216,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>104</v>
       </c>
@@ -2222,7 +2224,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>104</v>
       </c>
@@ -2230,7 +2232,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>104</v>
       </c>
@@ -2238,7 +2240,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>104</v>
       </c>
@@ -2246,7 +2248,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>104</v>
       </c>
@@ -2254,7 +2256,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>104</v>
       </c>
@@ -2262,7 +2264,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>104</v>
       </c>
@@ -2270,7 +2272,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>104</v>
       </c>
@@ -2278,7 +2280,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>104</v>
       </c>
@@ -2286,7 +2288,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>104</v>
       </c>
@@ -2294,7 +2296,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>104</v>
       </c>
@@ -2302,7 +2304,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>104</v>
       </c>
@@ -2310,7 +2312,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>104</v>
       </c>
@@ -2318,7 +2320,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>104</v>
       </c>
@@ -2326,7 +2328,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>104</v>
       </c>
@@ -2334,7 +2336,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>104</v>
       </c>
@@ -2342,7 +2344,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>104</v>
       </c>
@@ -2350,7 +2352,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>104</v>
       </c>
@@ -2358,7 +2360,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>104</v>
       </c>
@@ -2366,7 +2368,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>104</v>
       </c>
@@ -2374,7 +2376,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>104</v>
       </c>
@@ -2382,7 +2384,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>104</v>
       </c>
@@ -2390,7 +2392,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>104</v>
       </c>
@@ -2398,7 +2400,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2">
         <v>104</v>
       </c>
@@ -2406,7 +2408,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="2">
         <v>104</v>
       </c>
@@ -2414,7 +2416,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2">
         <v>104</v>
       </c>
@@ -2422,7 +2424,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="2">
         <v>104</v>
       </c>
@@ -2430,7 +2432,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2">
         <v>104</v>
       </c>
@@ -2438,7 +2440,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="2">
         <v>104</v>
       </c>
@@ -2446,7 +2448,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2">
         <v>104</v>
       </c>
@@ -2454,7 +2456,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="2">
         <v>104</v>
       </c>
@@ -2462,7 +2464,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2">
         <v>104</v>
       </c>
@@ -2470,7 +2472,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="2">
         <v>104</v>
       </c>
@@ -2478,7 +2480,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2">
         <v>104</v>
       </c>
@@ -2486,7 +2488,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="2">
         <v>104</v>
       </c>
@@ -2494,7 +2496,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="2">
         <v>104</v>
       </c>
@@ -2502,7 +2504,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="2">
         <v>104</v>
       </c>
@@ -2510,7 +2512,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="2">
         <v>104</v>
       </c>
@@ -2518,7 +2520,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="2">
         <v>104</v>
       </c>
@@ -2526,7 +2528,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2">
         <v>104</v>
       </c>
@@ -2534,7 +2536,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="2">
         <v>104</v>
       </c>
@@ -2542,7 +2544,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2">
         <v>104</v>
       </c>
@@ -2550,7 +2552,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="2">
         <v>104</v>
       </c>
@@ -2558,7 +2560,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2">
         <v>104</v>
       </c>
@@ -2566,7 +2568,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="2">
         <v>104</v>
       </c>
@@ -2574,7 +2576,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2">
         <v>104</v>
       </c>
@@ -2582,7 +2584,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>104</v>
       </c>
@@ -2590,7 +2592,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>104</v>
       </c>
@@ -2598,7 +2600,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>104</v>
       </c>
@@ -2606,7 +2608,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>104</v>
       </c>
@@ -2614,7 +2616,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>104</v>
       </c>
@@ -2622,7 +2624,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="273" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>104</v>
       </c>
@@ -2630,7 +2632,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="274" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>104</v>
       </c>
@@ -2638,7 +2640,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="275" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>104</v>
       </c>
@@ -2646,7 +2648,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="276" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>104</v>
       </c>
@@ -2654,7 +2656,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="277" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>104</v>
       </c>
@@ -2662,7 +2664,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="278" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>104</v>
       </c>
@@ -2670,7 +2672,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="279" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>104</v>
       </c>
@@ -2678,7 +2680,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="280" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>104</v>
       </c>
@@ -2686,7 +2688,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="281" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>104</v>
       </c>
@@ -2694,7 +2696,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="282" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>104</v>
       </c>
@@ -2702,7 +2704,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="283" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>104</v>
       </c>
@@ -2710,7 +2712,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="284" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>104</v>
       </c>
@@ -2718,7 +2720,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="285" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>104</v>
       </c>
@@ -2726,7 +2728,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="286" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>104</v>
       </c>
@@ -2734,7 +2736,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="287" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>105</v>
       </c>
@@ -2742,7 +2744,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>105</v>
       </c>
@@ -2750,7 +2752,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="289" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>105</v>
       </c>
@@ -2758,7 +2760,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="290" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>105</v>
       </c>
@@ -2766,7 +2768,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>105</v>
       </c>
@@ -2774,7 +2776,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="292" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>105</v>
       </c>
@@ -2782,7 +2784,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="293" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>105</v>
       </c>
@@ -2790,7 +2792,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="294" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>105</v>
       </c>
@@ -2798,7 +2800,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="295" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>105</v>
       </c>
@@ -2806,7 +2808,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="296" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>105</v>
       </c>
@@ -2814,7 +2816,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="297" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>105</v>
       </c>
@@ -2822,7 +2824,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="298" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>105</v>
       </c>
@@ -2830,7 +2832,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="299" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>105</v>
       </c>
@@ -2838,7 +2840,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="300" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
         <v>105</v>
       </c>
@@ -2846,7 +2848,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="301" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
         <v>105</v>
       </c>
@@ -2854,7 +2856,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="302" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>105</v>
       </c>
@@ -2862,7 +2864,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>105</v>
       </c>
@@ -2870,7 +2872,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>105</v>
       </c>
@@ -2878,7 +2880,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="305" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2">
         <v>105</v>
       </c>
@@ -2886,7 +2888,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="306" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2">
         <v>105</v>
       </c>
@@ -2894,7 +2896,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="307" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2">
         <v>105</v>
       </c>
@@ -2902,7 +2904,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="308" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2">
         <v>105</v>
       </c>
@@ -2910,7 +2912,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="309" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2">
         <v>105</v>
       </c>
@@ -2918,7 +2920,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="310" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2">
         <v>105</v>
       </c>
@@ -2926,7 +2928,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="311" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2">
         <v>105</v>
       </c>
@@ -2934,7 +2936,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="312" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2">
         <v>105</v>
       </c>
@@ -2942,7 +2944,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="313" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2">
         <v>105</v>
       </c>
@@ -2950,7 +2952,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="314" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="2">
         <v>105</v>
       </c>
@@ -2958,7 +2960,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="315" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="2">
         <v>105</v>
       </c>
@@ -2966,7 +2968,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="316" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="2">
         <v>105</v>
       </c>
@@ -2974,7 +2976,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="317" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="2">
         <v>105</v>
       </c>
@@ -2982,7 +2984,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="318" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="2">
         <v>105</v>
       </c>
@@ -2990,7 +2992,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="319" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="2">
         <v>105</v>
       </c>
@@ -2998,7 +3000,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="320" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="2">
         <v>105</v>
       </c>
@@ -3006,7 +3008,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="2">
         <v>105</v>
       </c>
@@ -3014,7 +3016,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="2">
         <v>105</v>
       </c>
@@ -3022,7 +3024,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="2">
         <v>105</v>
       </c>
@@ -3030,7 +3032,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="2">
         <v>105</v>
       </c>
@@ -3038,7 +3040,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="2">
         <v>105</v>
       </c>
@@ -3046,7 +3048,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="2">
         <v>105</v>
       </c>
@@ -3054,7 +3056,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2">
         <v>105</v>
       </c>
@@ -3062,7 +3064,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="2">
         <v>105</v>
       </c>
@@ -3070,7 +3072,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2">
         <v>105</v>
       </c>
@@ -3078,7 +3080,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="2">
         <v>105</v>
       </c>
@@ -3086,7 +3088,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2">
         <v>105</v>
       </c>
@@ -3094,7 +3096,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="2">
         <v>105</v>
       </c>
@@ -3102,7 +3104,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2">
         <v>105</v>
       </c>
@@ -3110,7 +3112,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="2">
         <v>105</v>
       </c>
@@ -3118,7 +3120,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2">
         <v>105</v>
       </c>
@@ -3126,7 +3128,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="2">
         <v>105</v>
       </c>
@@ -3134,7 +3136,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2">
         <v>105</v>
       </c>
@@ -3142,7 +3144,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="2">
         <v>105</v>
       </c>
@@ -3150,7 +3152,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="2">
         <v>105</v>
       </c>
@@ -3158,7 +3160,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="2">
         <v>105</v>
       </c>
@@ -3166,7 +3168,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="2">
         <v>105</v>
       </c>
@@ -3174,7 +3176,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="2">
         <v>105</v>
       </c>
@@ -3182,7 +3184,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="2">
         <v>105</v>
       </c>
@@ -3190,7 +3192,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="2">
         <v>105</v>
       </c>
@@ -3198,7 +3200,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="2">
         <v>105</v>
       </c>
@@ -3206,7 +3208,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="2">
         <v>105</v>
       </c>
@@ -3214,7 +3216,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="2">
         <v>105</v>
       </c>
@@ -3222,7 +3224,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="2">
         <v>105</v>
       </c>
@@ -3230,7 +3232,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="2">
         <v>105</v>
       </c>
@@ -3238,7 +3240,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="2">
         <v>105</v>
       </c>
@@ -3246,7 +3248,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2">
         <v>105</v>
       </c>
@@ -3254,7 +3256,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="2">
         <v>105</v>
       </c>
@@ -3262,7 +3264,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="353" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2">
         <v>105</v>
       </c>
@@ -3270,7 +3272,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="354" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="2">
         <v>105</v>
       </c>
@@ -3278,7 +3280,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="355" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="2">
         <v>105</v>
       </c>
@@ -3286,7 +3288,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="356" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="2">
         <v>105</v>
       </c>
@@ -3294,7 +3296,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="357" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="2">
         <v>105</v>
       </c>
@@ -3302,7 +3304,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="358" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="2">
         <v>105</v>
       </c>
@@ -3310,7 +3312,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="359" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2">
         <v>106</v>
       </c>
@@ -3318,7 +3320,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="360" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="2">
         <v>106</v>
       </c>
@@ -3326,7 +3328,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="361" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2">
         <v>106</v>
       </c>
@@ -3334,7 +3336,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="362" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="2">
         <v>106</v>
       </c>
@@ -3342,7 +3344,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="363" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="2">
         <v>106</v>
       </c>
@@ -3350,7 +3352,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="364" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="2">
         <v>106</v>
       </c>
@@ -3358,7 +3360,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="365" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="2">
         <v>106</v>
       </c>
@@ -3366,7 +3368,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="2">
         <v>106</v>
       </c>
@@ -3374,7 +3376,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="2">
         <v>106</v>
       </c>
@@ -3382,7 +3384,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="368" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="2">
         <v>106</v>
       </c>
@@ -3390,7 +3392,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="369" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="2">
         <v>106</v>
       </c>
@@ -3398,7 +3400,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="370" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="2">
         <v>106</v>
       </c>
@@ -3406,7 +3408,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="371" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="2">
         <v>106</v>
       </c>
@@ -3414,7 +3416,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="372" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="2">
         <v>106</v>
       </c>
@@ -3422,7 +3424,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="373" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="2">
         <v>106</v>
       </c>
@@ -3430,7 +3432,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="374" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="2">
         <v>106</v>
       </c>
@@ -3438,7 +3440,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="375" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2">
         <v>106</v>
       </c>
@@ -3446,7 +3448,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="376" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="2">
         <v>106</v>
       </c>
@@ -3454,7 +3456,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="377" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
         <v>106</v>
       </c>
@@ -3462,7 +3464,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="378" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="2">
         <v>106</v>
       </c>
@@ -3470,7 +3472,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="379" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="2">
         <v>106</v>
       </c>
@@ -3478,7 +3480,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="380" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="2">
         <v>106</v>
       </c>
@@ -3486,7 +3488,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="381" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2">
         <v>106</v>
       </c>
@@ -3494,7 +3496,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="382" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="2">
         <v>106</v>
       </c>
@@ -3502,7 +3504,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="383" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2">
         <v>106</v>
       </c>
@@ -3510,7 +3512,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="384" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="2">
         <v>106</v>
       </c>
@@ -3518,7 +3520,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="385" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2">
         <v>106</v>
       </c>
@@ -3526,7 +3528,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="386" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="2">
         <v>106</v>
       </c>
@@ -3534,7 +3536,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="387" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="2">
         <v>106</v>
       </c>
@@ -3542,7 +3544,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="388" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="2">
         <v>106</v>
       </c>
@@ -3550,7 +3552,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="389" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="2">
         <v>106</v>
       </c>
@@ -3558,7 +3560,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="390" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="2">
         <v>106</v>
       </c>
@@ -3566,7 +3568,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="391" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="2">
         <v>106</v>
       </c>
@@ -3574,7 +3576,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="392" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="2">
         <v>106</v>
       </c>
@@ -3582,7 +3584,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="393" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="2">
         <v>106</v>
       </c>
@@ -3590,7 +3592,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="394" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="2">
         <v>106</v>
       </c>
@@ -3598,7 +3600,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="395" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="2">
         <v>106</v>
       </c>
@@ -3606,7 +3608,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="396" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="2">
         <v>106</v>
       </c>
@@ -3614,7 +3616,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="397" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="2">
         <v>106</v>
       </c>
@@ -3622,7 +3624,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="398" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="2">
         <v>106</v>
       </c>
@@ -3630,7 +3632,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="399" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="2">
         <v>106</v>
       </c>
@@ -3638,7 +3640,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="400" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="2">
         <v>106</v>
       </c>
@@ -3646,7 +3648,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="401" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2">
         <v>106</v>
       </c>
@@ -3654,7 +3656,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="402" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="2">
         <v>106</v>
       </c>
@@ -3662,7 +3664,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="403" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2">
         <v>106</v>
       </c>
@@ -3670,7 +3672,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="404" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="2">
         <v>106</v>
       </c>
@@ -3678,7 +3680,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="405" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="2">
         <v>106</v>
       </c>
@@ -3686,7 +3688,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="406" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="2">
         <v>106</v>
       </c>
@@ -3694,7 +3696,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="407" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="2">
         <v>106</v>
       </c>
@@ -3702,7 +3704,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="408" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="2">
         <v>106</v>
       </c>
@@ -3710,7 +3712,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="409" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="2">
         <v>106</v>
       </c>
@@ -3718,7 +3720,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="410" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="2">
         <v>106</v>
       </c>
@@ -3726,7 +3728,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="411" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="2">
         <v>106</v>
       </c>
@@ -3734,7 +3736,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="412" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="2">
         <v>106</v>
       </c>
@@ -3742,7 +3744,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="413" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="2">
         <v>106</v>
       </c>
@@ -3750,7 +3752,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="414" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="2">
         <v>106</v>
       </c>
@@ -3758,7 +3760,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="415" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="2">
         <v>106</v>
       </c>
@@ -3766,7 +3768,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="416" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="2">
         <v>106</v>
       </c>
@@ -3774,7 +3776,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="417" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="2">
         <v>106</v>
       </c>
@@ -3782,7 +3784,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="418" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="2">
         <v>106</v>
       </c>
@@ -3790,7 +3792,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="419" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="2">
         <v>106</v>
       </c>
@@ -3798,7 +3800,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="420" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="2">
         <v>106</v>
       </c>
@@ -3806,7 +3808,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="421" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="2">
         <v>106</v>
       </c>
@@ -3814,7 +3816,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="422" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="2">
         <v>106</v>
       </c>
@@ -3822,7 +3824,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="423" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2">
         <v>106</v>
       </c>
@@ -3830,7 +3832,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="424" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="2">
         <v>106</v>
       </c>
@@ -3838,7 +3840,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="425" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2">
         <v>106</v>
       </c>
@@ -3846,7 +3848,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="426" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="2">
         <v>106</v>
       </c>
@@ -3854,7 +3856,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="427" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2">
         <v>106</v>
       </c>
@@ -3862,7 +3864,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="428" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="2">
         <v>106</v>
       </c>
@@ -3870,7 +3872,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="429" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="2">
         <v>106</v>
       </c>
@@ -3878,7 +3880,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="430" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="2">
         <v>106</v>
       </c>
@@ -3886,7 +3888,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="431" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2">
         <v>106</v>
       </c>
@@ -3894,7 +3896,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="432" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="2">
         <v>106</v>
       </c>
@@ -3902,7 +3904,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="433" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2">
         <v>106</v>
       </c>
@@ -3910,7 +3912,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="434" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="2">
         <v>106</v>
       </c>
@@ -3918,7 +3920,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="435" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="2">
         <v>106</v>
       </c>
@@ -3926,7 +3928,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="436" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="2">
         <v>106</v>
       </c>
@@ -3934,7 +3936,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="437" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="2">
         <v>106</v>
       </c>
@@ -3942,7 +3944,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="438" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="2">
         <v>106</v>
       </c>
@@ -3950,7 +3952,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="439" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="2">
         <v>106</v>
       </c>
@@ -3958,7 +3960,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="440" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="2">
         <v>106</v>
       </c>
@@ -3966,7 +3968,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="441" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="2">
         <v>106</v>
       </c>
@@ -3974,7 +3976,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="442" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="2">
         <v>106</v>
       </c>
@@ -3982,7 +3984,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="443" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="2">
         <v>106</v>
       </c>
@@ -3990,7 +3992,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="444" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="2">
         <v>107</v>
       </c>
@@ -3998,7 +4000,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="445" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="2">
         <v>107</v>
       </c>
@@ -4006,7 +4008,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="446" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="2">
         <v>107</v>
       </c>
@@ -4014,7 +4016,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="447" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2">
         <v>107</v>
       </c>
@@ -4022,7 +4024,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="448" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="2">
         <v>107</v>
       </c>
@@ -4030,7 +4032,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="449" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2">
         <v>107</v>
       </c>
@@ -4038,7 +4040,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="450" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="2">
         <v>107</v>
       </c>
@@ -4046,7 +4048,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="451" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2">
         <v>107</v>
       </c>
@@ -4054,7 +4056,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="452" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="2">
         <v>107</v>
       </c>
@@ -4062,7 +4064,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="453" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2">
         <v>107</v>
       </c>
@@ -4070,7 +4072,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="454" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="2">
         <v>107</v>
       </c>
@@ -4078,7 +4080,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="455" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2">
         <v>107</v>
       </c>
@@ -4086,7 +4088,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="456" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="2">
         <v>107</v>
       </c>
@@ -4094,7 +4096,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="457" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2">
         <v>107</v>
       </c>
@@ -4102,7 +4104,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="458" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="2">
         <v>107</v>
       </c>
@@ -4110,7 +4112,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="459" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="2">
         <v>107</v>
       </c>
@@ -4118,7 +4120,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="460" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="2">
         <v>107</v>
       </c>
@@ -4126,7 +4128,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="461" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="2">
         <v>107</v>
       </c>
@@ -4134,7 +4136,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="462" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="2">
         <v>107</v>
       </c>
@@ -4142,7 +4144,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="463" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="2">
         <v>107</v>
       </c>
@@ -4150,7 +4152,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="464" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="2">
         <v>107</v>
       </c>
@@ -4158,7 +4160,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="465" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="2">
         <v>107</v>
       </c>
@@ -4166,7 +4168,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="466" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="2">
         <v>107</v>
       </c>
@@ -4174,7 +4176,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="467" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2">
         <v>107</v>
       </c>
@@ -4182,7 +4184,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="468" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="2">
         <v>107</v>
       </c>
@@ -4190,7 +4192,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="469" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="2">
         <v>107</v>
       </c>
@@ -4198,7 +4200,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="470" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="2">
         <v>107</v>
       </c>
@@ -4206,7 +4208,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="471" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="2">
         <v>107</v>
       </c>
@@ -4214,7 +4216,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="472" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="2">
         <v>107</v>
       </c>
@@ -4222,7 +4224,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="473" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="2">
         <v>107</v>
       </c>
@@ -4230,7 +4232,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="474" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="2">
         <v>107</v>
       </c>
@@ -4238,7 +4240,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="475" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="2">
         <v>107</v>
       </c>
@@ -4246,7 +4248,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="476" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="2">
         <v>107</v>
       </c>
@@ -4254,7 +4256,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="477" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="2">
         <v>107</v>
       </c>
@@ -4262,7 +4264,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="478" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="2">
         <v>107</v>
       </c>
@@ -4270,7 +4272,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="479" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="2">
         <v>107</v>
       </c>
@@ -4278,7 +4280,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="480" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="2">
         <v>107</v>
       </c>
@@ -4286,7 +4288,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="481" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="2">
         <v>107</v>
       </c>
@@ -4294,7 +4296,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="482" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="2">
         <v>107</v>
       </c>
@@ -4302,7 +4304,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="483" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="2">
         <v>107</v>
       </c>
@@ -4310,7 +4312,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="484" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="2">
         <v>107</v>
       </c>
@@ -4318,7 +4320,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="485" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="2">
         <v>107</v>
       </c>
@@ -4326,7 +4328,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="486" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="2">
         <v>107</v>
       </c>
@@ -4334,7 +4336,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="487" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="2">
         <v>107</v>
       </c>
@@ -4342,7 +4344,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="488" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="2">
         <v>107</v>
       </c>
@@ -4350,7 +4352,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="489" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="2">
         <v>107</v>
       </c>
@@ -4358,7 +4360,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="490" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="2">
         <v>107</v>
       </c>
@@ -4366,7 +4368,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="491" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="2">
         <v>107</v>
       </c>
@@ -4374,7 +4376,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="492" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="2">
         <v>107</v>
       </c>
@@ -4382,7 +4384,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="493" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="2">
         <v>107</v>
       </c>
@@ -4390,7 +4392,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="494" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="2">
         <v>107</v>
       </c>
@@ -4398,7 +4400,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="495" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="2">
         <v>107</v>
       </c>
@@ -4406,7 +4408,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="496" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="2">
         <v>107</v>
       </c>
@@ -4414,7 +4416,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="497" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="2">
         <v>107</v>
       </c>
@@ -4422,7 +4424,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="498" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="2">
         <v>107</v>
       </c>
@@ -4430,7 +4432,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="499" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="2">
         <v>107</v>
       </c>
@@ -4438,7 +4440,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="500" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="2">
         <v>107</v>
       </c>
@@ -4446,7 +4448,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="501" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="2">
         <v>107</v>
       </c>
@@ -4454,7 +4456,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="502" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="2">
         <v>107</v>
       </c>
@@ -4462,7 +4464,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="503" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="2">
         <v>107</v>
       </c>
@@ -4470,7 +4472,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="504" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="2">
         <v>107</v>
       </c>
@@ -4478,7 +4480,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="505" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="2">
         <v>107</v>
       </c>
@@ -4486,7 +4488,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="506" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="2">
         <v>107</v>
       </c>
@@ -4494,7 +4496,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="507" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="2">
         <v>107</v>
       </c>
@@ -4502,7 +4504,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="508" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" s="2">
         <v>107</v>
       </c>
@@ -4510,7 +4512,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="509" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A509" s="2">
         <v>107</v>
       </c>
@@ -4518,7 +4520,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="510" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" s="2">
         <v>107</v>
       </c>
@@ -4526,7 +4528,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="511" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" s="2">
         <v>107</v>
       </c>
@@ -4534,7 +4536,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="512" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A512" s="2">
         <v>107</v>
       </c>
@@ -4542,7 +4544,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="513" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A513" s="2">
         <v>107</v>
       </c>
@@ -4550,7 +4552,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="514" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" s="2">
         <v>107</v>
       </c>
@@ -4558,7 +4560,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="515" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" s="2">
         <v>107</v>
       </c>
@@ -4566,7 +4568,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="516" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" s="2">
         <v>108</v>
       </c>
@@ -4574,7 +4576,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="517" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" s="2">
         <v>108</v>
       </c>
@@ -4582,7 +4584,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="518" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" s="2">
         <v>108</v>
       </c>
@@ -4590,7 +4592,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="519" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" s="2">
         <v>108</v>
       </c>
@@ -4598,7 +4600,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="520" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" s="2">
         <v>108</v>
       </c>
@@ -4606,7 +4608,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="521" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A521" s="2">
         <v>108</v>
       </c>
@@ -4614,7 +4616,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="522" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" s="2">
         <v>108</v>
       </c>
@@ -4622,7 +4624,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="523" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" s="2">
         <v>108</v>
       </c>
@@ -4630,7 +4632,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="524" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" s="2">
         <v>108</v>
       </c>
@@ -4638,7 +4640,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="525" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" s="2">
         <v>108</v>
       </c>
@@ -4646,7 +4648,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="526" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" s="2">
         <v>108</v>
       </c>
@@ -4654,7 +4656,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="527" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" s="2">
         <v>108</v>
       </c>
@@ -4662,7 +4664,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="528" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" s="2">
         <v>108</v>
       </c>
@@ -4670,7 +4672,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="529" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" s="2">
         <v>108</v>
       </c>
@@ -4678,7 +4680,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="530" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A530" s="2">
         <v>108</v>
       </c>
@@ -4686,7 +4688,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="531" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" s="2">
         <v>108</v>
       </c>
@@ -4694,7 +4696,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="532" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" s="2">
         <v>108</v>
       </c>
@@ -4702,7 +4704,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="533" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" s="2">
         <v>108</v>
       </c>
@@ -4710,7 +4712,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="534" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" s="2">
         <v>108</v>
       </c>
@@ -4718,7 +4720,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="535" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" s="2">
         <v>108</v>
       </c>
@@ -4726,7 +4728,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="536" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" s="2">
         <v>108</v>
       </c>
@@ -4734,7 +4736,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="537" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" s="2">
         <v>108</v>
       </c>
@@ -4742,7 +4744,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="538" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A538" s="2">
         <v>108</v>
       </c>
@@ -4750,7 +4752,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="539" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" s="2">
         <v>108</v>
       </c>
@@ -4758,7 +4760,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="540" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" s="2">
         <v>108</v>
       </c>
@@ -4766,7 +4768,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="541" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" s="2">
         <v>108</v>
       </c>
@@ -4774,7 +4776,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="542" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" s="2">
         <v>108</v>
       </c>
@@ -4782,7 +4784,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="543" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" s="2">
         <v>108</v>
       </c>
@@ -4790,7 +4792,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="544" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" s="2">
         <v>108</v>
       </c>
@@ -4798,7 +4800,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="545" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" s="2">
         <v>108</v>
       </c>
@@ -4806,7 +4808,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="546" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" s="2">
         <v>108</v>
       </c>
@@ -4814,7 +4816,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="547" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A547" s="2">
         <v>108</v>
       </c>
@@ -4822,7 +4824,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="548" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" s="2">
         <v>108</v>
       </c>
@@ -4830,7 +4832,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="549" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" s="2">
         <v>108</v>
       </c>
@@ -4838,7 +4840,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="550" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" s="2">
         <v>108</v>
       </c>
@@ -4846,7 +4848,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="551" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" s="2">
         <v>108</v>
       </c>
@@ -4854,7 +4856,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="552" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" s="2">
         <v>108</v>
       </c>
@@ -4862,7 +4864,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="553" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" s="2">
         <v>108</v>
       </c>
@@ -4870,7 +4872,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="554" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" s="2">
         <v>108</v>
       </c>
@@ -4878,7 +4880,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="555" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" s="2">
         <v>108</v>
       </c>
@@ -4886,7 +4888,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="556" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" s="2">
         <v>108</v>
       </c>
@@ -4894,7 +4896,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="557" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" s="2">
         <v>108</v>
       </c>
@@ -4902,7 +4904,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="558" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" s="2">
         <v>108</v>
       </c>
@@ -4910,7 +4912,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="559" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" s="2">
         <v>108</v>
       </c>
@@ -4918,7 +4920,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="560" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" s="2">
         <v>108</v>
       </c>
@@ -4926,7 +4928,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="561" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" s="2">
         <v>108</v>
       </c>
@@ -4934,7 +4936,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="562" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" s="2">
         <v>108</v>
       </c>
@@ -4942,7 +4944,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="563" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" s="2">
         <v>108</v>
       </c>
@@ -4950,7 +4952,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="564" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" s="2">
         <v>108</v>
       </c>
@@ -4958,7 +4960,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="565" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" s="2">
         <v>108</v>
       </c>
@@ -4966,7 +4968,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="566" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" s="2">
         <v>108</v>
       </c>
@@ -4974,7 +4976,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="567" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" s="2">
         <v>108</v>
       </c>
@@ -4982,7 +4984,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="568" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" s="2">
         <v>108</v>
       </c>
@@ -4990,7 +4992,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="569" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" s="2">
         <v>108</v>
       </c>
@@ -4998,7 +5000,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="570" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" s="2">
         <v>108</v>
       </c>
@@ -5006,7 +5008,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="571" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A571" s="2">
         <v>108</v>
       </c>
@@ -5014,7 +5016,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="572" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A572" s="2">
         <v>108</v>
       </c>
@@ -5022,7 +5024,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="573" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A573" s="2">
         <v>108</v>
       </c>
@@ -5030,7 +5032,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="574" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A574" s="2">
         <v>108</v>
       </c>
@@ -5038,7 +5040,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="575" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A575" s="2">
         <v>108</v>
       </c>
@@ -5046,7 +5048,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="576" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A576" s="2">
         <v>108</v>
       </c>
@@ -5054,7 +5056,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="577" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A577" s="2">
         <v>108</v>
       </c>
@@ -5062,7 +5064,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="578" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A578" s="2">
         <v>108</v>
       </c>
@@ -5070,7 +5072,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="579" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A579" s="2">
         <v>108</v>
       </c>
@@ -5078,7 +5080,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="580" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A580" s="2">
         <v>108</v>
       </c>
@@ -5086,7 +5088,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="581" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A581" s="2">
         <v>108</v>
       </c>
@@ -5094,7 +5096,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="582" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A582" s="2">
         <v>108</v>
       </c>
@@ -5102,7 +5104,7 @@
         <v>2401</v>
       </c>
     </row>
-    <row r="583" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A583" s="2">
         <v>108</v>
       </c>
@@ -5110,7 +5112,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="584" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A584" s="2">
         <v>108</v>
       </c>
@@ -5118,7 +5120,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="585" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A585" s="2">
         <v>108</v>
       </c>
@@ -5126,7 +5128,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="586" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A586" s="2">
         <v>108</v>
       </c>
@@ -5134,7 +5136,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="587" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A587" s="2">
         <v>108</v>
       </c>
@@ -5142,7 +5144,7 @@
         <v>2503</v>
       </c>
     </row>
-    <row r="588" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A588" s="2">
         <v>109</v>
       </c>
@@ -5150,7 +5152,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="589" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A589" s="2">
         <v>109</v>
       </c>
@@ -5158,7 +5160,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="590" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A590" s="2">
         <v>109</v>
       </c>
@@ -5166,7 +5168,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="591" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A591" s="2">
         <v>109</v>
       </c>
@@ -5174,7 +5176,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="592" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A592" s="2">
         <v>109</v>
       </c>
@@ -5182,7 +5184,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="593" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A593" s="2">
         <v>109</v>
       </c>
@@ -5190,7 +5192,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="594" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A594" s="2">
         <v>109</v>
       </c>
@@ -5198,7 +5200,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="595" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A595" s="2">
         <v>109</v>
       </c>
@@ -5206,7 +5208,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="596" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A596" s="2">
         <v>109</v>
       </c>
@@ -5214,7 +5216,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="597" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" s="2">
         <v>109</v>
       </c>
@@ -5222,7 +5224,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="598" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A598" s="2">
         <v>109</v>
       </c>
@@ -5230,7 +5232,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="599" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A599" s="2">
         <v>109</v>
       </c>
@@ -5238,7 +5240,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="600" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A600" s="2">
         <v>109</v>
       </c>
@@ -5246,7 +5248,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="601" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A601" s="2">
         <v>109</v>
       </c>
@@ -5254,7 +5256,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="602" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A602" s="2">
         <v>109</v>
       </c>
@@ -5262,7 +5264,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="603" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A603" s="2">
         <v>109</v>
       </c>
@@ -5270,7 +5272,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="604" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A604" s="2">
         <v>109</v>
       </c>
@@ -5278,7 +5280,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="605" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A605" s="2">
         <v>109</v>
       </c>
@@ -5286,7 +5288,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="606" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A606" s="2">
         <v>109</v>
       </c>
@@ -5294,7 +5296,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="607" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A607" s="2">
         <v>109</v>
       </c>
@@ -5302,7 +5304,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="608" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A608" s="2">
         <v>109</v>
       </c>
@@ -5310,7 +5312,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="609" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A609" s="2">
         <v>109</v>
       </c>
@@ -5318,7 +5320,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="610" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A610" s="2">
         <v>109</v>
       </c>
@@ -5326,7 +5328,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="611" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A611" s="2">
         <v>109</v>
       </c>
@@ -5334,7 +5336,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="612" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A612" s="2">
         <v>109</v>
       </c>
@@ -5342,7 +5344,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="613" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A613" s="2">
         <v>109</v>
       </c>
@@ -5350,7 +5352,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="614" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A614" s="2">
         <v>109</v>
       </c>
@@ -5358,7 +5360,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="615" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A615" s="2">
         <v>109</v>
       </c>
@@ -5366,7 +5368,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="616" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A616" s="2">
         <v>109</v>
       </c>
@@ -5374,7 +5376,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="617" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A617" s="2">
         <v>109</v>
       </c>
@@ -5382,7 +5384,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="618" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A618" s="2">
         <v>109</v>
       </c>
@@ -5390,7 +5392,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="619" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A619" s="2">
         <v>109</v>
       </c>
@@ -5398,7 +5400,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="620" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A620" s="2">
         <v>109</v>
       </c>
@@ -5406,7 +5408,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="621" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A621" s="2">
         <v>109</v>
       </c>
@@ -5414,7 +5416,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="622" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A622" s="2">
         <v>109</v>
       </c>
@@ -5422,7 +5424,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="623" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A623" s="2">
         <v>109</v>
       </c>
@@ -5430,7 +5432,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="624" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A624" s="2">
         <v>109</v>
       </c>
@@ -5438,7 +5440,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="625" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A625" s="2">
         <v>109</v>
       </c>
@@ -5446,7 +5448,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="626" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A626" s="2">
         <v>109</v>
       </c>
@@ -5454,7 +5456,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="627" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A627" s="2">
         <v>109</v>
       </c>
@@ -5462,7 +5464,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="628" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A628" s="2">
         <v>109</v>
       </c>
@@ -5470,7 +5472,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="629" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A629" s="2">
         <v>109</v>
       </c>
@@ -5478,7 +5480,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="630" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A630" s="2">
         <v>109</v>
       </c>
@@ -5486,7 +5488,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="631" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A631" s="2">
         <v>109</v>
       </c>
@@ -5494,7 +5496,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="632" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A632" s="2">
         <v>109</v>
       </c>
@@ -5502,7 +5504,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="633" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A633" s="2">
         <v>109</v>
       </c>
@@ -5510,7 +5512,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="634" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A634" s="2">
         <v>109</v>
       </c>
@@ -5518,7 +5520,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="635" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A635" s="2">
         <v>109</v>
       </c>
@@ -5526,7 +5528,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="636" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A636" s="2">
         <v>109</v>
       </c>
@@ -5534,7 +5536,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="637" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A637" s="2">
         <v>109</v>
       </c>
@@ -5542,7 +5544,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="638" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A638" s="2">
         <v>109</v>
       </c>
@@ -5550,7 +5552,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="639" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A639" s="2">
         <v>109</v>
       </c>
@@ -5558,7 +5560,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="640" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A640" s="2">
         <v>109</v>
       </c>
@@ -5566,7 +5568,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="641" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A641" s="2">
         <v>109</v>
       </c>
@@ -5574,7 +5576,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="642" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A642" s="2">
         <v>109</v>
       </c>
@@ -5582,7 +5584,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="643" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A643" s="2">
         <v>109</v>
       </c>
@@ -5590,7 +5592,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="644" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A644" s="2">
         <v>109</v>
       </c>
@@ -5598,7 +5600,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="645" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A645" s="2">
         <v>109</v>
       </c>
@@ -5606,7 +5608,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="646" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A646" s="2">
         <v>109</v>
       </c>
@@ -5614,7 +5616,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="647" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A647" s="2">
         <v>109</v>
       </c>
@@ -5622,7 +5624,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="648" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A648" s="2">
         <v>109</v>
       </c>
@@ -5630,7 +5632,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="649" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A649" s="2">
         <v>109</v>
       </c>
@@ -5638,7 +5640,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="650" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A650" s="2">
         <v>109</v>
       </c>
@@ -5646,7 +5648,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="651" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" s="2">
         <v>109</v>
       </c>
@@ -5654,7 +5656,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="652" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A652" s="2">
         <v>109</v>
       </c>
@@ -5662,7 +5664,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="653" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A653" s="2">
         <v>109</v>
       </c>
@@ -5670,7 +5672,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="654" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A654" s="2">
         <v>109</v>
       </c>
@@ -5678,7 +5680,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="655" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A655" s="2">
         <v>109</v>
       </c>
@@ -5686,7 +5688,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="656" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A656" s="2">
         <v>109</v>
       </c>
@@ -5694,7 +5696,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="657" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" s="2">
         <v>109</v>
       </c>
@@ -5702,7 +5704,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="658" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A658" s="2">
         <v>109</v>
       </c>
@@ -5710,7 +5712,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="659" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A659" s="2">
         <v>109</v>
       </c>
@@ -5718,7 +5720,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="660" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A660" s="2">
         <v>109</v>
       </c>
@@ -5726,7 +5728,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="661" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A661" s="2">
         <v>109</v>
       </c>
@@ -5734,7 +5736,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="662" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A662" s="2">
         <v>109</v>
       </c>
@@ -5742,7 +5744,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="663" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A663" s="2">
         <v>109</v>
       </c>
@@ -5750,7 +5752,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="664" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A664" s="2">
         <v>109</v>
       </c>
@@ -5758,7 +5760,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="665" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A665" s="2">
         <v>109</v>
       </c>
@@ -5766,7 +5768,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="666" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A666" s="2">
         <v>109</v>
       </c>
@@ -5774,7 +5776,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="667" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A667" s="2">
         <v>109</v>
       </c>
@@ -5782,7 +5784,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="668" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A668" s="2">
         <v>109</v>
       </c>
@@ -5790,7 +5792,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="669" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A669" s="2">
         <v>109</v>
       </c>
@@ -5798,7 +5800,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="670" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A670" s="2">
         <v>109</v>
       </c>
@@ -5806,7 +5808,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="671" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A671" s="2">
         <v>109</v>
       </c>
@@ -5814,7 +5816,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="672" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A672" s="2">
         <v>109</v>
       </c>
@@ -5822,7 +5824,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="673" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A673" s="2">
         <v>109</v>
       </c>
@@ -5830,7 +5832,7 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="674" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A674" s="2">
         <v>110</v>
       </c>
@@ -5838,7 +5840,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="675" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A675" s="2">
         <v>110</v>
       </c>
@@ -5846,7 +5848,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="676" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A676" s="2">
         <v>110</v>
       </c>
@@ -5854,7 +5856,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="677" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A677" s="2">
         <v>110</v>
       </c>
@@ -5862,7 +5864,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="678" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A678" s="2">
         <v>110</v>
       </c>
@@ -5870,7 +5872,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="679" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A679" s="2">
         <v>110</v>
       </c>
@@ -5878,7 +5880,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="680" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" s="2">
         <v>110</v>
       </c>
@@ -5886,7 +5888,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="681" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A681" s="2">
         <v>110</v>
       </c>
@@ -5894,7 +5896,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="682" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A682" s="2">
         <v>110</v>
       </c>
@@ -5902,7 +5904,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="683" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A683" s="2">
         <v>110</v>
       </c>
@@ -5910,7 +5912,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="684" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A684" s="2">
         <v>110</v>
       </c>
@@ -5918,7 +5920,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="685" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A685" s="2">
         <v>110</v>
       </c>
@@ -5926,7 +5928,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="686" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A686" s="2">
         <v>110</v>
       </c>
@@ -5934,7 +5936,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="687" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A687" s="2">
         <v>110</v>
       </c>
@@ -5942,7 +5944,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="688" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A688" s="2">
         <v>110</v>
       </c>
@@ -5950,7 +5952,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="689" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A689" s="2">
         <v>110</v>
       </c>
@@ -5958,7 +5960,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="690" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A690" s="2">
         <v>110</v>
       </c>
@@ -5966,7 +5968,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="691" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A691" s="2">
         <v>110</v>
       </c>
@@ -5974,7 +5976,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="692" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A692" s="2">
         <v>110</v>
       </c>
@@ -5982,7 +5984,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="693" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A693" s="2">
         <v>110</v>
       </c>
@@ -5990,7 +5992,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="694" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" s="2">
         <v>110</v>
       </c>
@@ -5998,7 +6000,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="695" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A695" s="2">
         <v>110</v>
       </c>
@@ -6006,7 +6008,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="696" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A696" s="2">
         <v>110</v>
       </c>
@@ -6014,7 +6016,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="697" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A697" s="2">
         <v>110</v>
       </c>
@@ -6022,7 +6024,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="698" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" s="2">
         <v>110</v>
       </c>
@@ -6030,7 +6032,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="699" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A699" s="2">
         <v>110</v>
       </c>
@@ -6038,7 +6040,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="700" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A700" s="2">
         <v>110</v>
       </c>
@@ -6046,7 +6048,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="701" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A701" s="2">
         <v>110</v>
       </c>
@@ -6054,7 +6056,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="702" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A702" s="2">
         <v>110</v>
       </c>
@@ -6062,7 +6064,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="703" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A703" s="2">
         <v>110</v>
       </c>
@@ -6070,7 +6072,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="704" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A704" s="2">
         <v>110</v>
       </c>
@@ -6078,7 +6080,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="705" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A705" s="2">
         <v>110</v>
       </c>
@@ -6086,7 +6088,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="706" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A706" s="2">
         <v>110</v>
       </c>
@@ -6094,7 +6096,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="707" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A707" s="2">
         <v>110</v>
       </c>
@@ -6102,7 +6104,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="708" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A708" s="2">
         <v>110</v>
       </c>
@@ -6110,7 +6112,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="709" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A709" s="2">
         <v>110</v>
       </c>
@@ -6118,7 +6120,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="710" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A710" s="2">
         <v>111</v>
       </c>
@@ -6126,7 +6128,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="711" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A711" s="2">
         <v>111</v>
       </c>
@@ -6134,7 +6136,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="712" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A712" s="2">
         <v>111</v>
       </c>
@@ -6142,7 +6144,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="713" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A713" s="2">
         <v>111</v>
       </c>
@@ -6150,7 +6152,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="714" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A714" s="2">
         <v>111</v>
       </c>
@@ -6158,7 +6160,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="715" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A715" s="2">
         <v>111</v>
       </c>
@@ -6166,7 +6168,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="716" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A716" s="2">
         <v>111</v>
       </c>
@@ -6174,7 +6176,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="717" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A717" s="2">
         <v>111</v>
       </c>
@@ -6182,7 +6184,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="718" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A718" s="2">
         <v>111</v>
       </c>
@@ -6190,7 +6192,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="719" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A719" s="2">
         <v>111</v>
       </c>
@@ -6198,7 +6200,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="720" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A720" s="2">
         <v>111</v>
       </c>
@@ -6206,7 +6208,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="721" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A721" s="2">
         <v>111</v>
       </c>
@@ -6214,7 +6216,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="722" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A722" s="2">
         <v>111</v>
       </c>
@@ -6222,7 +6224,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="723" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A723" s="2">
         <v>111</v>
       </c>
@@ -6230,7 +6232,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="724" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A724" s="2">
         <v>111</v>
       </c>
@@ -6238,7 +6240,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="725" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A725" s="2">
         <v>111</v>
       </c>
@@ -6246,7 +6248,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="726" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A726" s="2">
         <v>111</v>
       </c>
@@ -6254,7 +6256,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="727" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A727" s="2">
         <v>111</v>
       </c>
@@ -6262,7 +6264,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="728" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A728" s="2">
         <v>111</v>
       </c>
@@ -6270,7 +6272,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="729" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A729" s="2">
         <v>111</v>
       </c>
@@ -6278,7 +6280,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="730" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A730" s="2">
         <v>111</v>
       </c>
@@ -6286,7 +6288,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="731" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A731" s="2">
         <v>111</v>
       </c>
@@ -6294,7 +6296,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="732" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A732" s="2">
         <v>111</v>
       </c>
@@ -6302,7 +6304,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="733" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A733" s="2">
         <v>111</v>
       </c>
@@ -6310,7 +6312,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="734" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A734" s="2">
         <v>111</v>
       </c>
@@ -6318,7 +6320,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="735" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A735" s="2">
         <v>111</v>
       </c>
@@ -6326,7 +6328,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="736" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A736" s="2">
         <v>111</v>
       </c>
@@ -6334,7 +6336,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="737" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A737" s="2">
         <v>111</v>
       </c>
@@ -6342,7 +6344,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="738" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A738" s="2">
         <v>111</v>
       </c>
@@ -6350,7 +6352,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="739" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A739" s="2">
         <v>111</v>
       </c>
@@ -6358,7 +6360,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="740" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" s="2">
         <v>111</v>
       </c>
@@ -6366,7 +6368,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="741" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A741" s="2">
         <v>111</v>
       </c>
@@ -6374,7 +6376,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="742" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A742" s="2">
         <v>111</v>
       </c>
@@ -6382,7 +6384,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="743" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A743" s="2">
         <v>111</v>
       </c>
@@ -6390,7 +6392,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="744" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" s="2">
         <v>111</v>
       </c>
@@ -6398,7 +6400,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="745" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A745" s="2">
         <v>111</v>
       </c>
@@ -6406,7 +6408,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="746" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A746" s="2">
         <v>111</v>
       </c>
@@ -6414,7 +6416,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="747" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A747" s="2">
         <v>111</v>
       </c>
@@ -6422,7 +6424,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="748" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A748" s="2">
         <v>111</v>
       </c>
@@ -6430,7 +6432,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="749" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A749" s="2">
         <v>111</v>
       </c>
@@ -6438,7 +6440,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="750" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A750" s="2">
         <v>111</v>
       </c>
@@ -6446,7 +6448,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="751" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A751" s="2">
         <v>111</v>
       </c>
@@ -6454,7 +6456,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="752" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A752" s="2">
         <v>111</v>
       </c>
@@ -6462,7 +6464,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="753" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A753" s="2">
         <v>111</v>
       </c>
@@ -6470,7 +6472,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="754" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A754" s="2">
         <v>111</v>
       </c>
@@ -6478,7 +6480,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="755" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A755" s="2">
         <v>111</v>
       </c>
@@ -6486,7 +6488,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="756" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A756" s="2">
         <v>111</v>
       </c>
@@ -6494,7 +6496,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="757" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A757" s="2">
         <v>111</v>
       </c>
@@ -6502,7 +6504,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="758" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A758" s="2">
         <v>111</v>
       </c>
@@ -6510,7 +6512,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="759" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A759" s="2">
         <v>111</v>
       </c>
@@ -6518,7 +6520,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="760" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A760" s="2">
         <v>111</v>
       </c>
@@ -6526,7 +6528,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="761" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A761" s="2">
         <v>111</v>
       </c>
@@ -6534,7 +6536,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="762" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A762" s="2">
         <v>111</v>
       </c>
@@ -6542,7 +6544,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="763" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A763" s="2">
         <v>111</v>
       </c>
@@ -6550,7 +6552,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="764" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A764" s="2">
         <v>111</v>
       </c>
@@ -6558,7 +6560,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="765" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A765" s="2">
         <v>111</v>
       </c>
@@ -6566,7 +6568,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="766" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A766" s="2">
         <v>112</v>
       </c>
@@ -6574,7 +6576,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="767" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A767" s="2">
         <v>112</v>
       </c>
@@ -6582,7 +6584,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="768" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A768" s="2">
         <v>112</v>
       </c>
@@ -6590,7 +6592,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="769" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A769" s="2">
         <v>112</v>
       </c>
@@ -6598,7 +6600,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="770" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A770" s="2">
         <v>112</v>
       </c>
@@ -6606,7 +6608,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="771" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A771" s="2">
         <v>112</v>
       </c>
@@ -6614,7 +6616,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="772" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A772" s="2">
         <v>112</v>
       </c>
@@ -6622,7 +6624,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="773" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A773" s="2">
         <v>112</v>
       </c>
@@ -6630,7 +6632,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="774" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A774" s="2">
         <v>112</v>
       </c>
@@ -6638,7 +6640,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="775" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A775" s="2">
         <v>112</v>
       </c>
@@ -6646,7 +6648,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="776" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A776" s="2">
         <v>112</v>
       </c>
@@ -6654,7 +6656,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="777" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A777" s="2">
         <v>112</v>
       </c>
@@ -6662,7 +6664,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="778" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A778" s="2">
         <v>112</v>
       </c>
@@ -6670,7 +6672,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="779" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A779" s="2">
         <v>112</v>
       </c>
@@ -6678,7 +6680,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="780" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A780" s="2">
         <v>112</v>
       </c>
@@ -6686,7 +6688,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="781" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A781" s="2">
         <v>112</v>
       </c>
@@ -6694,7 +6696,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="782" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A782" s="2">
         <v>112</v>
       </c>
@@ -6702,7 +6704,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="783" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A783" s="2">
         <v>112</v>
       </c>
@@ -6710,7 +6712,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="784" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A784" s="2">
         <v>112</v>
       </c>
@@ -6718,7 +6720,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="785" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A785" s="2">
         <v>112</v>
       </c>
@@ -6726,7 +6728,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="786" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A786" s="2">
         <v>112</v>
       </c>
@@ -6734,7 +6736,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="787" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A787" s="2">
         <v>112</v>
       </c>
@@ -6742,7 +6744,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="788" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A788" s="2">
         <v>112</v>
       </c>
@@ -6750,7 +6752,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="789" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A789" s="2">
         <v>112</v>
       </c>
@@ -6758,7 +6760,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="790" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A790" s="2">
         <v>112</v>
       </c>
@@ -6766,7 +6768,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="791" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A791" s="2">
         <v>112</v>
       </c>
@@ -6774,7 +6776,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="792" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A792" s="2">
         <v>112</v>
       </c>
@@ -6782,7 +6784,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="793" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A793" s="2">
         <v>112</v>
       </c>
@@ -6790,7 +6792,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="794" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A794" s="2">
         <v>112</v>
       </c>
@@ -6798,7 +6800,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="795" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A795" s="2">
         <v>112</v>
       </c>
@@ -6806,7 +6808,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="796" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A796" s="2">
         <v>112</v>
       </c>
@@ -6814,7 +6816,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="797" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A797" s="2">
         <v>112</v>
       </c>
@@ -6822,7 +6824,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="798" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A798" s="2">
         <v>112</v>
       </c>
@@ -6830,7 +6832,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="799" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A799" s="2">
         <v>112</v>
       </c>
@@ -6838,7 +6840,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="800" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A800" s="2">
         <v>112</v>
       </c>
@@ -6846,7 +6848,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="801" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A801" s="2">
         <v>112</v>
       </c>
@@ -6854,7 +6856,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="802" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A802" s="2">
         <v>112</v>
       </c>
@@ -6862,7 +6864,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="803" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A803" s="2">
         <v>112</v>
       </c>
@@ -6870,7 +6872,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="804" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A804" s="2">
         <v>112</v>
       </c>
@@ -6878,7 +6880,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="805" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A805" s="2">
         <v>112</v>
       </c>
@@ -6886,7 +6888,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="806" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A806" s="2">
         <v>112</v>
       </c>
@@ -6894,7 +6896,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="807" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A807" s="2">
         <v>112</v>
       </c>
@@ -6902,7 +6904,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="808" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A808" s="2">
         <v>112</v>
       </c>
@@ -6910,7 +6912,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="809" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A809" s="2">
         <v>112</v>
       </c>
@@ -6918,7 +6920,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="810" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A810" s="2">
         <v>112</v>
       </c>
@@ -6926,7 +6928,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="811" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A811" s="2">
         <v>112</v>
       </c>
@@ -6934,7 +6936,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="812" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A812" s="2">
         <v>112</v>
       </c>
@@ -6942,7 +6944,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="813" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A813" s="2">
         <v>112</v>
       </c>
@@ -6950,7 +6952,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="814" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A814" s="2">
         <v>112</v>
       </c>
@@ -6958,7 +6960,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="815" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A815" s="2">
         <v>112</v>
       </c>
@@ -6966,7 +6968,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="816" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A816" s="2">
         <v>112</v>
       </c>
@@ -6974,7 +6976,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="817" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A817" s="2">
         <v>112</v>
       </c>
@@ -6982,7 +6984,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="818" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A818" s="2">
         <v>112</v>
       </c>
@@ -6990,7 +6992,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="819" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A819" s="2">
         <v>112</v>
       </c>
@@ -6998,7 +7000,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="820" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A820" s="2">
         <v>112</v>
       </c>
@@ -7006,7 +7008,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="821" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A821" s="2">
         <v>112</v>
       </c>
@@ -7014,7 +7016,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="822" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A822" s="2">
         <v>112</v>
       </c>
@@ -7022,7 +7024,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="823" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A823" s="2">
         <v>112</v>
       </c>
@@ -7030,7 +7032,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="824" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A824" s="2">
         <v>112</v>
       </c>
@@ -7038,7 +7040,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="825" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A825" s="2">
         <v>112</v>
       </c>
@@ -7046,7 +7048,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="826" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A826" s="2">
         <v>112</v>
       </c>
@@ -7054,7 +7056,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="827" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A827" s="2">
         <v>112</v>
       </c>
@@ -7062,7 +7064,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="828" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A828" s="2">
         <v>112</v>
       </c>
@@ -7070,7 +7072,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="829" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A829" s="2">
         <v>112</v>
       </c>
@@ -7078,7 +7080,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="830" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A830" s="2">
         <v>112</v>
       </c>
@@ -7086,7 +7088,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="831" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A831" s="2">
         <v>112</v>
       </c>
@@ -7094,7 +7096,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="832" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A832" s="2">
         <v>112</v>
       </c>
@@ -7102,7 +7104,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="833" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A833" s="2">
         <v>112</v>
       </c>
@@ -7110,7 +7112,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="834" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A834" s="2">
         <v>112</v>
       </c>
@@ -7118,7 +7120,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="835" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A835" s="2">
         <v>112</v>
       </c>
@@ -7126,7 +7128,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="836" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A836" s="2">
         <v>112</v>
       </c>
@@ -7134,7 +7136,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="837" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A837" s="2">
         <v>112</v>
       </c>
@@ -7142,7 +7144,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="838" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A838" s="2">
         <v>112</v>
       </c>
@@ -7150,7 +7152,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="839" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A839" s="2">
         <v>112</v>
       </c>
@@ -7158,7 +7160,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="840" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A840" s="2">
         <v>112</v>
       </c>
@@ -7166,7 +7168,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="841" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A841" s="2">
         <v>112</v>
       </c>
@@ -7174,7 +7176,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="842" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A842" s="2">
         <v>112</v>
       </c>
@@ -7182,7 +7184,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="843" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A843" s="2">
         <v>112</v>
       </c>
@@ -7190,7 +7192,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="844" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A844" s="2">
         <v>112</v>
       </c>
@@ -7198,7 +7200,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="845" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A845" s="2">
         <v>112</v>
       </c>
@@ -7206,7 +7208,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="846" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A846" s="2">
         <v>112</v>
       </c>
@@ -7214,7 +7216,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="847" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A847" s="2">
         <v>112</v>
       </c>
@@ -7222,7 +7224,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="848" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A848" s="2">
         <v>112</v>
       </c>
@@ -7230,7 +7232,7 @@
         <v>2203</v>
       </c>
     </row>
-    <row r="849" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A849" s="2">
         <v>112</v>
       </c>
@@ -7238,7 +7240,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="850" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A850" s="2">
         <v>112</v>
       </c>
@@ -7246,7 +7248,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="851" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="851" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A851" s="2">
         <v>112</v>
       </c>
@@ -7254,84 +7256,84 @@
         <v>2304</v>
       </c>
     </row>
-    <row r="852" spans="1:2" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A852" s="2">
         <v>999</v>
       </c>
       <c r="B852" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="853" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A853" s="2">
         <v>999</v>
       </c>
       <c r="B853" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="854" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="854" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A854" s="2">
         <v>999</v>
       </c>
       <c r="B854" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="855" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="855" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A855" s="2">
         <v>999</v>
       </c>
       <c r="B855" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="856" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="856" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A856" s="2">
         <v>999</v>
       </c>
       <c r="B856" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="857" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A857" s="2">
         <v>999</v>
       </c>
       <c r="B857" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="858" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="858" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A858" s="2">
         <v>999</v>
       </c>
       <c r="B858" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="859" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="859" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A859" s="2">
         <v>999</v>
       </c>
       <c r="B859" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="860" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A860" s="2">
         <v>999</v>
       </c>
       <c r="B860" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="861" spans="1:2" ht="15.6" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="861" spans="1:2" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A861" s="2">
         <v>999</v>
       </c>
       <c r="B861" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
